--- a/plc/s7-1x00/core/motion-control/EMotionControlCommands-v1.0.xlsx
+++ b/plc/s7-1x00/core/motion-control/EMotionControlCommands-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\motion-control\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27ABBAD5-C4FD-47DA-9075-D2535881CCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D4FC26-E039-487A-B65C-E1BBF75248C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10230" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="39">
   <si>
     <t>Name</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>Accessibility</t>
+  </si>
+  <si>
+    <t>Bool</t>
+  </si>
+  <si>
+    <t>EMotionControlCommands</t>
+  </si>
+  <si>
+    <t>{"version":"v1.0","author":"cyanezf","family":"core/motion-control","status":"deprecated","deprecatedBy":"EMotionControlCommands-v1.1","dependencies":[]}</t>
   </si>
 </sst>
 </file>
@@ -477,10 +486,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="38.453125" customWidth="1"/>
+    <col min="2" max="2" width="42.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="101.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -502,24 +513,24 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
@@ -528,7 +539,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -536,7 +547,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
@@ -545,7 +556,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -553,7 +564,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -562,7 +573,7 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -570,7 +581,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
@@ -579,7 +590,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -587,7 +598,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
@@ -596,7 +607,7 @@
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -604,7 +615,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
@@ -613,7 +624,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -621,7 +632,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
@@ -630,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -638,7 +649,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>6</v>
@@ -647,7 +658,7 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -655,7 +666,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
         <v>6</v>
@@ -664,7 +675,7 @@
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -672,7 +683,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
         <v>6</v>
@@ -681,7 +692,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -689,7 +700,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
         <v>6</v>
@@ -698,7 +709,7 @@
         <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -706,18 +717,35 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
         <v>33</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>9</v>
       </c>
     </row>
